--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -957,134 +957,134 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
+          <t>[안산시글로벌청소년센터] 사회참여통합팀 팀원 채용 공고</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>무기계약직,비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
-        </is>
-      </c>
+          <t>경기도 안산시</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
-        </is>
-      </c>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067293</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>무기계약직,비정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>이음</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>임상심리치료전문인력 채용</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1145,12 +1145,134 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -743,25 +743,29 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -771,7 +775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -782,17 +786,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -804,216 +808,192 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,대졸(4년)</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
-        </is>
-      </c>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066330</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,고졸</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
-        </is>
-      </c>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지 · 행정</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>무기계약직,비정규직</t>
+          <t>정규직,비정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울,경기</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
+          <t>학력무관,대졸(4년)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1023,41 +1003,45 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1067,151 +1051,366 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://cw.careerlink.kr</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>한국청소년상담복지개발원</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>이음</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>임상심리치료전문인력 채용</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>용인시처인장애인복지관</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>계약직</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>경기도</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>복지넷</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1034,28 +1034,28 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>이음</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>임상심리치료전문인력 채용</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1116,28 +1116,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1149,25 +1149,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1177,28 +1177,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1210,12 +1210,73 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -815,136 +815,128 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>도봉구청소년상담복지센터</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,대졸(4년)</t>
-        </is>
-      </c>
+          <t>서울특별시 도봉구</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
-        </is>
-      </c>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>청소년 · 복지 · 행정</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>정규직,비정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+          <t>서울,경기</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>학력무관,고졸</t>
+          <t>학력무관,대졸(4년)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -954,70 +946,70 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>학력무관</t>
+          <t>학력무관,고졸</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1027,35 +1019,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://cw.careerlink.kr</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>관악청소년자립지원관(이용형,들꽃)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 관악구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1066,17 +1058,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1088,117 +1080,129 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>D-9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1210,35 +1214,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1249,17 +1253,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-19</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1271,12 +1275,195 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>이음</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>임상심리치료전문인력 채용</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,14 +589,14 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -606,22 +606,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>도봉구청소년상담복지센터</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 도봉구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -632,17 +632,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -654,14 +654,14 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -671,22 +671,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>도봉구청소년상담복지센터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 도봉구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -697,17 +697,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
@@ -994,28 +994,28 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1048,56 +1048,56 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,12 +1170,138 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>파트타임</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -933,28 +933,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -965,17 +965,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -987,35 +987,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1048,35 +1048,35 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,56 +1109,56 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,25 +1170,25 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1198,28 +1198,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1231,60 +1231,56 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>용인시처인장애인복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1296,12 +1292,260 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>파트타임</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>(사)대전지체장애인협회 중구지회</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>사회복지사 상담사 긴급 모집</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,17 +567,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,29 +589,25 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>도봉구청소년상담복지센터</t>
+          <t>관악청소년자립지원관(이용형,들꽃)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
+          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 도봉구</t>
+          <t>서울특별시 관악구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -632,12 +628,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -654,173 +650,169 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>행정 · 교육</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,고졸</t>
-        </is>
-      </c>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
-        </is>
-      </c>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃)</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -831,17 +823,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -853,108 +845,96 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 금천구</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -965,17 +945,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -987,35 +967,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>용인시처인장애인복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,17 +1006,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1048,56 +1028,60 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>오산시아동보호전문기관</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>파트타임</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>경기도 오산시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,35 +1093,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>대전해바라기센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1148,17 +1132,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,56 +1154,56 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>(사)대전지체장애인협회 중구지회</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>사회복지사 상담사 긴급 모집</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1231,25 +1215,25 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>솔이랑</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1259,7 +1243,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1270,17 +1254,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1292,260 +1276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>오산시아동보호전문기관</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>파트타임</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>경기도 오산시</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>대전해바라기센터</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>(사)대전지체장애인협회 중구지회</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>사회복지사 상담사 긴급 모집</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>솔이랑</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>D-15</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,17 +567,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,25 +589,29 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃)</t>
+          <t>도봉구청소년상담복지센터</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
+          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -617,7 +621,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구</t>
+          <t>서울특별시 도봉구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -628,12 +632,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -650,169 +654,173 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 노원구</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직 · 무기직 · 체험형 인턴 · 계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://cw.careerlink.kr</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>관악청소년자립지원관(이용형,들꽃)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 관악구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -823,17 +831,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -845,96 +853,108 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -945,17 +965,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -967,35 +987,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1006,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1028,60 +1048,56 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1093,35 +1109,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>대전해바라기센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1132,17 +1148,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1154,56 +1170,56 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>(사)대전지체장애인협회 중구지회</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>사회복지사 상담사 긴급 모집</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1215,25 +1231,25 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>솔이랑</t>
+          <t>용인시처인장애인복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1243,7 +1259,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1254,17 +1270,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1276,12 +1292,260 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>시간제</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>(사)대전지체장애인협회 중구지회</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>사회복지사 상담사 긴급 모집</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -567,17 +567,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
@@ -599,50 +599,46 @@
           <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>도봉구청소년상담복지센터</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직 · 대체인력</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 도봉구</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -654,39 +650,35 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>관악청소년자립지원관(이용형,들꽃)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 관악구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -697,17 +689,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -719,70 +711,70 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직 · 무기직 · 체험형 인턴 · 계약직 · 대체인력</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>학력무관,고졸</t>
+          <t>학력무관</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+          <t>없음</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -792,7 +784,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
@@ -805,12 +797,12 @@
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃)</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -820,7 +812,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -831,17 +823,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -853,80 +845,68 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직 · 대체인력</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
@@ -939,12 +919,12 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -954,7 +934,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -965,17 +945,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -987,25 +967,25 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1015,7 +995,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,17 +1006,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1048,25 +1028,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>용인시처인장애인복지관</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1076,7 +1056,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1087,17 +1067,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,7 +1089,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1102,12 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1137,7 +1117,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1148,17 +1128,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,56 +1150,60 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>오산시아동보호전문기관</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도 오산시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1231,35 +1215,35 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 파주시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1270,17 +1254,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1292,60 +1276,56 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>시간제</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1357,7 +1337,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1386,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1467,7 +1447,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1528,7 +1508,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직 · 대체인력</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -663,12 +663,12 @@
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃)</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -689,17 +689,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -711,80 +711,68 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>계약직 · 대체인력</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
@@ -797,12 +785,12 @@
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -812,7 +800,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -823,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -845,25 +833,25 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -873,7 +861,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -884,17 +872,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -906,56 +894,60 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>오산시아동보호전문기관</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>파트타임</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>경기도 오산시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -967,25 +959,25 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -995,68 +987,80 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>부산,경기,전남광주,경남,제주</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,석사,박사</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>해당사항 없음 해당사항 없음</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 파주시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1067,17 +1071,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1089,35 +1093,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1128,17 +1132,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
@@ -1160,50 +1164,46 @@
           <t>상담 · 청소년</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>솔이랑</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>시간제</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1215,317 +1215,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>경기북부청소년성문화센터</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>경기도 파주시</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>청소년 · 복지 · 교육</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>율목종합사회복지관</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안양시 만안구</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>D-15</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>대전해바라기센터</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>(사)대전지체장애인협회 중구지회</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>사회복지사 상담사 긴급 모집</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>솔이랑</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -10,7 +10,7 @@
     <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -760,7 +760,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -901,48 +901,48 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>교육</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>부산,경기,전남광주,경남,제주</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,석사,박사</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -950,34 +950,42 @@
           <t>D-1</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>해당사항 없음 해당사항 없음</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
+          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -987,80 +995,68 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>부산,경기,전남광주,경남,제주</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,석사,박사</t>
-        </is>
-      </c>
+          <t>경기도 파주시</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>해당사항 없음 해당사항 없음</t>
-        </is>
-      </c>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1071,17 +1067,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1093,25 +1089,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>솔이랑</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1121,7 +1117,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1132,17 +1128,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1154,73 +1150,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>솔이랑</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,32 +531,24 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>의정부시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용공고</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -567,17 +559,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,25 +581,29 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -617,28 +613,28 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 동대문구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -650,56 +646,56 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -711,56 +707,56 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>정규직 · 대체인력</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,7 +768,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
@@ -785,12 +781,12 @@
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -800,7 +796,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +807,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,25 +829,25 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -861,7 +857,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +868,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,98 +890,86 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>부산,경기,전남광주,경남,제주</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,석사,박사</t>
-        </is>
-      </c>
+          <t>서울특별시 금천구</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>해당사항 없음 해당사항 없음</t>
-        </is>
-      </c>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1006,17 +990,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1028,41 +1012,45 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>부산,경기,전남광주,경남,제주</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,석사,박사</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1072,52 +1060,60 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>해당사항 없음 해당사항 없음</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>솔이랑</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 파주시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1150,12 +1146,378 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>시흥시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>안양시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>율목종합사회복지관</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
@@ -531,24 +531,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>의정부시남자단기청소년쉼터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용공고</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -559,17 +567,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -581,29 +589,25 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -613,23 +617,23 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -646,7 +650,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
@@ -669,7 +673,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직 · 대체인력</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -714,49 +718,49 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직 · 대체인력</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 동대문구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -768,35 +772,35 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -807,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -829,35 +833,35 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -868,7 +872,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -890,35 +894,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -929,17 +933,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -951,86 +955,98 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>서울,부산,인천</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1040,70 +1056,58 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>부산,경기,전남광주,경남,제주</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,석사,박사</t>
-        </is>
-      </c>
+          <t>경기도 파주시</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>해당사항 없음 해당사항 없음</t>
-        </is>
-      </c>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1113,7 +1117,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1124,17 +1128,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1146,7 +1150,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1163,12 @@
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>안양시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1174,7 +1178,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1207,35 +1211,35 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1268,38 +1272,42 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>복지 · 행정</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1307,7 +1315,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1317,19 +1325,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1394,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1439,7 +1455,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1500,7 +1516,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직 · 대체인력</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -711,35 +711,31 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>의정부시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용 연장공고</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -750,17 +746,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,35 +768,35 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>학교밖청소년 대안교육기관 내일더하기</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +807,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,25 +829,29 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +872,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,35 +894,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -933,17 +933,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -955,108 +955,96 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,인천</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
-        </is>
-      </c>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1067,17 +1055,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1089,7 +1077,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1090,12 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1117,7 +1105,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1128,17 +1116,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1150,96 +1138,104 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>서울,부산,인천</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1250,17 +1246,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1272,42 +1268,38 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>청년인턴(체험형)</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 파주시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1315,60 +1307,52 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
-        </is>
-      </c>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1384,17 +1368,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1406,7 +1390,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1403,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>솔이랑</t>
+          <t>안양시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1445,17 +1429,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1467,25 +1451,25 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1495,7 +1479,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1506,17 +1490,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1528,12 +1512,809 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>복지 · 행정</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>학교법인한국폴리텍</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>체험형 인턴</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>마음드림심리상담센터 광명점</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>경기도 광명시</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>경기도 용인시</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>경기해바라기센터(아동)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>시간제</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>안산시장애인복지관</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 단원구</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>안산시장애인복지관</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>빅사랑</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 상록구</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,32 +531,24 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>의정부시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용 연장공고</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -567,17 +559,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,56 +581,56 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관</t>
+          <t>학교밖청소년 대안교육기관 내일더하기</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
+          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계약직 · 대체인력</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 동대문구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -650,56 +642,60 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>정규직 · 대체인력</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 동대문구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -711,92 +707,104 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>의정부시남자단기청소년쉼터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용 연장공고</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>서울,부산,인천</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
+          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -807,17 +815,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-35</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -829,39 +837,35 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +876,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,35 +898,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>안양시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -933,17 +937,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -955,35 +959,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -994,12 +998,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1016,38 +1020,42 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>복지 · 행정</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1055,12 +1063,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1068,65 +1076,73 @@
           <t>D-1</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1138,25 +1154,25 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1166,27 +1182,23 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,인천</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 용인시</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1194,48 +1206,44 @@
           <t>D-4</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
-        </is>
-      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1246,17 +1254,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-39</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1268,7 +1276,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1289,22 @@
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1307,17 +1315,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1329,7 +1337,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1350,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>파트타임</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1368,17 +1376,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1390,25 +1398,25 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1418,7 +1426,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1429,17 +1437,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1451,35 +1459,31 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1490,17 +1494,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1512,42 +1516,38 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>체험형 인턴</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 안산시 상록구</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1560,50 +1560,42 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
-        </is>
-      </c>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>아담중증장애인거주시설</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1613,23 +1605,23 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
+          <t>대전광역시 유성구</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1646,56 +1638,56 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>여성인권지원상담소 '느티나무'</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -1707,7 +1699,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
         </is>
       </c>
     </row>
@@ -1720,43 +1712,39 @@
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>여성인권지원상담소'느티나무'</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>대전광역시</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -1768,553 +1756,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안양시</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>경기해바라기센터(아동)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>시간제</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>안산시장애인복지관</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안산시 단원구</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>안산시장애인복지관</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>경기도</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>빅사랑</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안산시 상록구</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>D-16</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>솔이랑</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>아담중증장애인거주시설</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 유성구</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소 '느티나무'</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소'느티나무'</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -714,158 +714,162 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,인천</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 노원구</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
-        </is>
-      </c>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>서울,부산,인천</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-35</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -876,17 +880,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -898,7 +902,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
@@ -911,12 +915,12 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -926,7 +930,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -937,7 +941,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -959,35 +963,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>안양시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1020,42 +1024,38 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>청년인턴(체험형)</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 안양시 만안구</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1076,85 +1076,89 @@
           <t>D-1</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>복지 · 행정</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>체험형 인턴</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1171,12 @@
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1182,28 +1186,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1215,25 +1219,25 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1243,28 +1247,28 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 용인시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1276,25 +1280,25 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1304,7 +1308,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1337,35 +1341,35 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1376,17 +1380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1398,35 +1402,35 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1442,12 +1446,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1459,31 +1463,35 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1494,7 +1502,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1516,25 +1524,25 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1544,7 +1552,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1560,12 +1568,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1598,18 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1621,12 +1625,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1638,25 +1642,25 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소 '느티나무'</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1666,13 +1670,13 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1682,12 +1686,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -1699,52 +1703,52 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소'느티나무'</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>대전광역시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -1756,12 +1760,191 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-9</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>D-9</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -760,7 +760,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -779,103 +779,91 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,인천</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
-        </is>
-      </c>
+          <t>D-32</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -885,12 +873,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-35</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -902,51 +890,51 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 용인시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -963,35 +951,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1002,17 +990,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1024,25 +1012,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1052,7 +1040,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1063,17 +1051,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1085,42 +1073,38 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>체험형 인턴</t>
+          <t>파트타임</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1133,81 +1117,73 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
-        </is>
-      </c>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1219,56 +1195,56 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1280,7 +1256,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1269,18 @@
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1319,17 +1291,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1341,35 +1313,35 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1380,17 +1352,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1402,35 +1374,31 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>시간제</t>
-        </is>
-      </c>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1441,17 +1409,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1463,35 +1431,35 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>아담중증장애인거주시설</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>대전광역시 유성구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1502,17 +1470,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1524,7 +1492,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1505,12 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>여성인권지원상담소 '느티나무'</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1552,13 +1520,13 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1573,7 +1541,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1585,7 +1553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
         </is>
       </c>
     </row>
@@ -1598,24 +1566,24 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>여성인권지원상담소'느티나무'</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>대전광역시</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1630,7 +1598,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1642,309 +1610,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>빅사랑</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안산시 상록구</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>수원희망의집</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>경기도</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>아담중증장애인거주시설</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 유성구</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D-7</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소 '느티나무'</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>D-9</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소'느티나무'</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>D-9</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O24"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -588,28 +588,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기</t>
+          <t>정립회관</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
+          <t>정립회관 육아휴직 대체 인력 채용 공고(장애인재활상담사/사회복지사)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시 광진구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -620,17 +620,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -642,29 +642,25 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 교육</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
+          <t>학교밖청소년 대안교육기관 내일더하기</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
+          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -685,17 +681,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -707,14 +703,14 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -724,22 +720,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -750,17 +746,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,31 +768,39 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -807,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -829,56 +833,56 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
+          <t>서울특별시 성북구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -890,56 +894,52 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-32</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -951,25 +951,25 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -979,28 +979,28 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1012,25 +1012,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1040,28 +1040,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 용인시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1073,35 +1073,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1134,35 +1134,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1195,35 +1195,35 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1256,31 +1256,35 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1313,25 +1317,25 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1341,7 +1345,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1357,12 +1361,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1374,25 +1378,25 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>수원희망의집</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1409,17 +1413,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1431,35 +1435,35 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1475,12 +1479,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1492,25 +1496,25 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소 '느티나무'</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1520,28 +1524,28 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1553,52 +1557,56 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소'느티나무'</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>대전광역시</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1610,12 +1618,252 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>시흥시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,21 +534,29 @@
           <t>청소년</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>의정부시남자단기청소년쉼터</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용 연장공고</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -559,17 +567,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -581,35 +589,39 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>정립회관</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>정립회관 육아휴직 대체 인력 채용 공고(장애인재활상담사/사회복지사)</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계약직 · 대체인력</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 광진구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -620,17 +632,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -642,35 +654,35 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071979</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시 성북구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -681,17 +693,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-35</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -703,39 +715,31 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -746,17 +750,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -768,39 +772,35 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,35 +833,35 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 가족</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 성북구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +872,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-39</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,31 +894,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>파트타임</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -929,17 +933,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -951,56 +955,56 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1012,56 +1016,56 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1073,7 +1077,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
@@ -1086,22 +1090,18 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1134,35 +1134,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1195,51 +1195,51 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>시간제</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1256,25 +1256,25 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1317,25 +1317,25 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1356,17 +1356,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
@@ -1391,18 +1391,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>아담중증장애인거주시설</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>대전광역시 유성구</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1418,12 +1422,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1435,25 +1439,25 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>여성인권지원상담소 '느티나무'</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1463,13 +1467,13 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>대전광역시 중구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1479,12 +1483,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1496,56 +1500,52 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개</t>
+          <t>여성인권지원상담소'느티나무'</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>경기도 김포시</t>
+          <t>대전광역시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1557,313 +1557,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>수원희망의집</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>경기도 수원시</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>시흥시남자단기청소년쉼터</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>아담중증장애인거주시설</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 유성구</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소 '느티나무'</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소'느티나무'</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,18 +661,18 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년 · 행정</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 가족</t>
+          <t>남양주시일시청소년쉼터</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
+          <t>남양주시일시청소년쉼터 직원(행정원)채용 공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 성북구</t>
+          <t>경기도 남양주시</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -693,17 +693,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-35</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074800</t>
         </is>
       </c>
     </row>
@@ -728,18 +728,22 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 성북구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -750,17 +754,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,35 +776,31 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-28</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,25 +833,25 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -894,35 +894,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -933,17 +933,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -955,35 +955,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -994,17 +994,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1016,25 +1016,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
@@ -1095,13 +1095,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1134,35 +1138,31 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1223,18 +1223,18 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 김포시</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1256,25 +1256,25 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>수원희망의집</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1284,28 +1284,28 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1317,35 +1317,31 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1356,17 +1352,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1378,35 +1374,35 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+          <t>[끌어올림] 아동청소년 그룹홈 생활보육사 1명 채용공고</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1417,17 +1413,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1439,25 +1435,25 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073938</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소 '느티나무'</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1467,28 +1463,28 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1500,52 +1496,56 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소'느티나무'</t>
+          <t>시립나래울아동청소년센터</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>화성시 시립 나래울아동청소년센터 사회복지사 채용 공고</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>대전광역시</t>
+          <t>경기도 화성시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1557,12 +1557,313 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074397</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 아토</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>아토) 아동 청소년 방과후 활동 제공인력 구인합니다. (경력자 관리자급)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 상록구</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>D-35</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075045</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>대전북부아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>대전북부아동보호전문기관 직원 채용 공고(상담원-육아휴직대체)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>계약직 · 대체인력</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075192</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -567,12 +567,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -589,29 +589,25 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 행정</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>남양주시일시청소년쉼터</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>남양주시일시청소년쉼터 직원(행정원)채용 공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>경기도 남양주시</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -632,17 +628,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -654,25 +650,25 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074800</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 행정</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>남양주시일시청소년쉼터</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>남양주시일시청소년쉼터 직원(행정원)채용 공고</t>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>경기도 남양주시</t>
+          <t>서울특별시 성북구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -693,17 +689,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-32</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -715,68 +711,80 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074800</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 가족</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
+          <t>한국기술교육대학교 직업능력심사평가원 기간제 근로자(휴직 및 퇴사 대체인력) 채용(6차) 공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 성북구</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-35</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ㅇ 국가공무원법 제33조의 결격사유가 없는 자 ㅇ 임용일 기준 한국기술교육대학교 「직원인사규정」제14조의 결격사유에 해당하지 않으며, 동 규정 제37조에 의한 정년연령(60세) 미만인 지원자 ㅇ 모집구분별 계약일로부터 현업 근무 가능자 ㅇ 채용분야 전산은 관련 자격증* 보유 필요 * 컴퓨터시스템응용기술사, 정보통신기술사, 정보관리기술사, 전자계산기기사, 정보통신기사, 정보처리기사, 정보보안기사 1개 이상 보유</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>취업지원대상자 관련법에 의거하여 가산점 반영 취업지원대상자 관련법에 의거하여 가산점 반영</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=859&amp;prefix_id=</t>
         </is>
       </c>
     </row>
@@ -821,7 +829,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -840,28 +848,28 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +880,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,56 +902,56 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -955,35 +963,31 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>시간제</t>
-        </is>
-      </c>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -994,17 +998,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1016,25 +1020,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>[끌어올림] 아동청소년 그룹홈 생활보육사 1명 채용공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1055,17 +1059,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1077,25 +1081,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073938</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1116,17 +1120,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1138,31 +1142,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>시립나래울아동청소년센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>화성시 시립 나래울아동청소년센터 사회복지사 채용 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 화성시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1173,17 +1181,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1195,30 +1203,30 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>주식회사 아토</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+          <t>아토) 아동 청소년 방과후 활동 제공인력 구인합니다. (경력자 관리자급)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1234,17 +1242,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1256,56 +1264,56 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075045</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개</t>
+          <t>대전북부아동보호전문기관</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
+          <t>대전북부아동보호전문기관 직원 채용 공고(상담원-육아휴직대체)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도 김포시</t>
+          <t>대전광역시 유성구</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1317,553 +1325,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>수원희망의집</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>경기도</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>수원희망의집</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>[끌어올림] 아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>경기도 수원시</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073938</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>시흥시남자단기청소년쉼터</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>시립나래울아동청소년센터</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>화성시 시립 나래울아동청소년센터 사회복지사 채용 공고</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>경기도 화성시</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>D-9</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074397</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>주식회사 아토</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>아토) 아동 청소년 방과후 활동 제공인력 구인합니다. (경력자 관리자급)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>경기도 안산시 상록구</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>D-35</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075045</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>아담중증장애인거주시설</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 유성구</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소 '느티나무'</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 중구</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-2</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 복지</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>여성인권지원상담소'느티나무'</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D-2</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>대전북부아동보호전문기관</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>대전북부아동보호전문기관 직원 채용 공고(상담원-육아휴직대체)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>계약직 · 대체인력</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>대전광역시 유성구</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075192</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/상담행정공고_최신.xlsx
+++ b/docs/files/상담행정공고_최신.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,25 +589,29 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068243</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 행정</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>남양주시일시청소년쉼터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>남양주시일시청소년쉼터 직원(행정원)채용 공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -617,7 +621,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>경기도 남양주시</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -628,17 +632,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -650,25 +654,25 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074800</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년 · 행정</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 가족</t>
+          <t>남양주시일시청소년쉼터</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
+          <t>남양주시일시청소년쉼터 직원(행정원)채용 공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -678,7 +682,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 성북구</t>
+          <t>경기도 남양주시</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -689,17 +693,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -711,137 +715,141 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074800</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 기간제 근로자(휴직 및 퇴사 대체인력) 채용(6차) 공고</t>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 성북구</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>ㅇ 국가공무원법 제33조의 결격사유가 없는 자 ㅇ 임용일 기준 한국기술교육대학교 「직원인사규정」제14조의 결격사유에 해당하지 않으며, 동 규정 제37조에 의한 정년연령(60세) 미만인 지원자 ㅇ 모집구분별 계약일로부터 현업 근무 가능자 ㅇ 채용분야 전산은 관련 자격증* 보유 필요 * 컴퓨터시스템응용기술사, 정보통신기술사, 정보관리기술사, 전자계산기기사, 정보통신기사, 정보처리기사, 정보보안기사 1개 이상 보유</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>취업지원대상자 관련법에 의거하여 가산점 반영 취업지원대상자 관련법에 의거하여 가산점 반영</t>
-        </is>
-      </c>
+          <t>D-32</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=859&amp;prefix_id=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>한국기술교육대학교 직업능력심사평가원 기간제 근로자(휴직 및 퇴사 대체인력) 채용(6차) 공고</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>계약직 · 대체인력</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>ㅇ 국가공무원법 제33조의 결격사유가 없는 자 ㅇ 임용일 기준 한국기술교육대학교 「직원인사규정」제14조의 결격사유에 해당하지 않으며, 동 규정 제37조에 의한 정년연령(60세) 미만인 지원자 ㅇ 모집구분별 계약일로부터 현업 근무 가능자 ㅇ 채용분야 전산은 관련 자격증* 보유 필요 * 컴퓨터시스템응용기술사, 정보통신기술사, 정보관리기술사, 전자계산기기사, 정보통신기사, 정보처리기사, 정보보안기사 1개 이상 보유</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>취업지원대상자 관련법에 의거하여 가산점 반영 취업지원대상자 관련법에 의거하여 가산점 반영</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=859&amp;prefix_id=</t>
         </is>
       </c>
     </row>
@@ -854,22 +862,18 @@
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -880,17 +884,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -902,7 +906,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
@@ -915,12 +919,12 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -930,18 +934,18 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 김포시</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -963,52 +967,56 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>수원희망의집</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1020,7 +1028,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1046,13 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>[끌어올림] 아동청소년 그룹홈 생활보육사 1명 채용공고</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1059,7 +1063,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1081,25 +1085,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073938</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>[끌어올림] 아동청소년 그룹홈 생활보육사 1명 채용공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1120,17 +1124,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1142,7 +1146,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073938</t>
         </is>
       </c>
     </row>
@@ -1210,18 +1214,18 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>주식회사 아토</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>아토) 아동 청소년 방과후 활동 제공인력 구인합니다. (경력자 관리자급)</t>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1231,28 +1235,28 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075045</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1281,22 @@
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>대전북부아동보호전문기관</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>대전북부아동보호전문기관 직원 채용 공고(상담원-육아휴직대체)</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1303,17 +1307,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1325,12 +1329,557 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>빛솔</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>오산시 학대피해아동쉼터(남아) 임상심리상담원(육아휴직 대체) 채용공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>대체인력</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075601</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>수원시청소년성문화센터</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>수원시청소년성문화센터 직원(팀원) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075791</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>김포시장애아동재활센터</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026년도 제5회 재활서비스 위탁 강사 채용 공고(놀이심리재활사)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>시간제</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>경기도 김포시</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075793</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 아토</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>아토) 아동 청소년 방과후 활동 제공인력 구인합니다. (경력자 관리자급)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 상록구</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>D-32</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075045</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>대전북부아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>대전북부아동보호전문기관 직원 채용 공고(상담원-육아휴직대체)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>계약직 · 대체인력</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075192</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>대전YWCA가족쉼터</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>대전YWCA가족쉼터 주거지원사업 상담원(계약직) 모집 공고</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075887</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>대전서부아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>대전서부아동보호전문기관 상담원 채용</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075721</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>세이브더칠드런 대전서부아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>대전서부아동보호전문기관 상담원 및 홈케어플래너서포터즈지원사업 지역관리자 모집</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 서구</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1075726</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
